--- a/data/trans_dic/IP31KM08_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM08_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,22; 53,21</t>
+          <t>21,89; 46,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,79; 41,25</t>
+          <t>30,99; 52,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,54; 43,63</t>
+          <t>29,83; 46,57</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,64; 52,56</t>
+          <t>45,76; 58,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,3; 57,72</t>
+          <t>41,11; 54,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,08; 53,21</t>
+          <t>45,3; 54,21</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,54; 52,12</t>
+          <t>35,25; 48,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,64; 48,15</t>
+          <t>40,1; 52,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,08; 48,07</t>
+          <t>39,3; 48,63</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>46,69%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,94; 47,15</t>
+          <t>39,72; 51,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,81; 51,8</t>
+          <t>41,12; 52,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,69; 48,41</t>
+          <t>42,6; 51,07</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,82; 46,72</t>
+          <t>42,18; 49,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,04; 48,56</t>
+          <t>42,87; 49,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,79; 46,73</t>
+          <t>43,31; 48,52</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>12458</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32926</t>
+          <t>30456</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14516; 24739</t>
+          <t>8195; 17236</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9416; 18680</t>
+          <t>13227; 22578</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26189; 40041</t>
+          <t>23896; 37310</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>116</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>74221</t>
+          <t>81781</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92944</t>
+          <t>68328</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>167165</t>
+          <t>150109</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63146; 83723</t>
+          <t>71858; 91800</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82420; 105034</t>
+          <t>59823; 78673</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>150422; 181588</t>
+          <t>137066; 164023</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>106</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78922</t>
+          <t>83680</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87384</t>
+          <t>81345</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166306</t>
+          <t>165025</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>66706; 90202</t>
+          <t>70537; 96677</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73599; 102314</t>
+          <t>70043; 92157</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146829; 185349</t>
+          <t>147308; 182277</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>149</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>109580</t>
+          <t>136346</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>139887</t>
+          <t>119285</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249467</t>
+          <t>255631</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76635; 129304</t>
+          <t>116072; 151853</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>118357; 157994</t>
+          <t>104998; 134353</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>212543; 280403</t>
+          <t>233282; 279647</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>406</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>282089</t>
+          <t>314265</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>286956</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>615865</t>
+          <t>601221</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>240513; 305116</t>
+          <t>289722; 339438</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>305651; 361634</t>
+          <t>265036; 307614</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>570122; 653213</t>
+          <t>565196; 633148</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM08_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM08_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman pasta o arroz casi a diario (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>33,28%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>42,17%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>38,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>21,89; 46,04</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30,99; 52,9</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>29,83; 46,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>52,08%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46,95%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>49,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>45,76; 58,46</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>41,11; 54,06</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>45,3; 54,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>41,81%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>46,57%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>44,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>35,25; 48,31</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>40,1; 52,76</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>39,3; 48,63</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>46,66%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>46,72%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>39,72; 51,97</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41,12; 52,62</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>42,6; 51,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>45,76%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>46,42%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>42,18; 49,42</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>42,87; 49,76</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>43,31; 48,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.3327897630791863</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4216978998439813</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.3801544723638767</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>12458</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17998</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30456</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.2189098797461264</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.3099043256458719</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.2982726018761715</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>8195; 17236</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13227; 22578</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>23896; 37310</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.460425444059483</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5289982104033439</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.4657039653586452</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5207601540684526</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4695495638632242</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.496130154355804</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>81781</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>68328</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>150109</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4575750417248841</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4111014551294633</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4530204879828225</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>71858; 91800</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>59823; 78673</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>137066; 164023</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5845548582136144</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5406380745851391</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5421182509912075</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4181364613672723</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4657008819349798</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4403035575695661</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>83680</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>81345</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>165025</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.3524640174369543</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.40099479034615</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3930320045265013</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>70537; 96677</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>70043; 92157</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>147308; 182277</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.4830798077337692</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5275999159972519</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.4863332668800188</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4665847689039056</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.467166421680684</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4668560051333002</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>136346</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>119285</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>255631</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.3972076291289447</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4112150582058782</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4260408000127158</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>116072; 151853</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>104998; 134353</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>233282; 279647</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5196523169077378</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5261774680628841</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5107161631951993</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>822</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.4575627130454269</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4641741812609337</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.460694638106942</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>314265</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>286956</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>601221</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.421827956503055</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.4287162446171972</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.4330902097975672</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>289722; 339438</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>265036; 307614</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>565196; 633148</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.4942146041384561</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4975903179044531</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.4851592107474283</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman pasta o arroz casi a diario (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>12458</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>17998</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>30456</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>8195</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>13227</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>23896</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>17236</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>22578</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>37310</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>81781</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>68328</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>150109</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>71858</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>59823</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>137066</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>91800</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>78673</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>164023</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>83680</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>81345</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>165025</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>70537</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>70043</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>147308</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>96677</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>92157</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>182277</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>149</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>136346</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>119285</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>255631</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>116072</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>104998</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>233282</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>151853</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>134353</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>279647</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>416</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>406</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>314265</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>286956</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>601221</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>289722</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>265036</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>565196</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>339438</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>307614</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>633148</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>